--- a/data-manipulation-scripts/sheets-cleanup/sheets/JUNCAO BICO INJETOR.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/JUNCAO BICO INJETOR.xlsx
@@ -572,8 +572,12 @@
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E10" s="8"/>
     </row>
     <row r="11">
